--- a/node/AlarmReport.xlsx
+++ b/node/AlarmReport.xlsx
@@ -120,27 +120,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ET366</t>
+          <t>ET061</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PORT_SPEDRO</t>
+          <t>MBADON_EXTENSION</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ET366_900</t>
+          <t>ET061</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>YOBSC02</t>
+          <t>ABBSC01</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -150,12 +150,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:35:17</t>
+          <t>2026-05-05 00:29:30</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:35:47</t>
+          <t>2026-05-05 00:29:30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -170,34 +170,34 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ET184</t>
+          <t>AC726</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CARR_ZEGBAN</t>
+          <t>ANGRE_PRGRME6</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ET184</t>
+          <t>AC726_900</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>YOBSC07</t>
+          <t>BVBSC04</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -207,12 +207,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:23:34</t>
+          <t>2026-05-05 06:53:32</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:23:34</t>
+          <t>2026-05-05 06:53:32</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -227,34 +227,34 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ET187</t>
+          <t>AC726</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HANNIE</t>
+          <t>ANGRE_PRGRME6</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ET187_900</t>
+          <t>AC726</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>YOBSC02</t>
+          <t>BVBSC04</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -264,12 +264,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:03:17</t>
+          <t>2026-05-05 06:53:32</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:03:17</t>
+          <t>2026-05-05 06:53:32</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -284,34 +284,34 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ET450</t>
+          <t>ET025</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SAYE</t>
+          <t>RESDCE_KIMI3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ET450</t>
+          <t>ET025_900</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>ABBSC03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -321,12 +321,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:03:08</t>
+          <t>2026-05-05 06:53:42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:03:08</t>
+          <t>2026-05-05 06:53:42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -341,34 +341,34 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ET219</t>
+          <t>AC386</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SOKO</t>
+          <t>21RRDT</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ET219_900</t>
+          <t>AC386_1800</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -378,12 +378,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:33:38</t>
+          <t>2026-05-05 08:27:26</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:33:38</t>
+          <t>2026-05-05 08:27:26</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -398,24 +398,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>ET416</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MATENIN</t>
+          <t>SAGBE_CELESTE</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>ET416_900</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -435,12 +435,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 08:27:26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 08:27:26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -462,27 +462,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>AC781</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MATENIN</t>
+          <t>GBAPET</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AC377_EXP</t>
+          <t>AC781</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AOBSC06</t>
+          <t>YOBSC02</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -492,12 +492,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 09:42:47</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 09:42:47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -507,39 +507,39 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ET418</t>
+          <t>ET493</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>AKEIKOI_GUEHABLE</t>
+          <t>ADIAPOTO</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ET418_1800</t>
+          <t>ET493</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>AOBSC06</t>
+          <t>YOBSC07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 10:44:34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:56</t>
+          <t>2026-05-05 10:44:34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -569,24 +569,24 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>KEKE TCHATCHA FERNANDEL</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AC374</t>
+          <t>ET713</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MATERNITE</t>
+          <t>ABOBO_SAGBE_RAIL</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AC374</t>
+          <t>ET713_900</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 11:28:26</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 11:28:26</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ET418</t>
+          <t>ET713</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>AKEIKOI_GUEHABLE</t>
+          <t>ABOBO_SAGBE_RAIL</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ET418_900</t>
+          <t>ET713_1800</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 11:28:26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 11:28:26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -683,34 +683,34 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>KEKE TCHATCHA FERNANDEL</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AC374</t>
+          <t>AC152</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MATERNITE</t>
+          <t>SOTREF</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AC374_EXP</t>
+          <t>AC152_900</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AOBSC06</t>
+          <t>YOBSC02</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 12:43:47</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:26</t>
+          <t>2026-05-05 12:43:47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -735,54 +735,54 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ET474</t>
+          <t>AC714</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DIO</t>
+          <t>DIDEROT</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ET474</t>
+          <t>AC714_900</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DAMBSC13</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:58</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:58:58</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -797,49 +797,49 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>IM276</t>
+          <t>AC373</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>DJELISSO_DIAWALA</t>
+          <t>VESSO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IM276</t>
+          <t>AC373_1800</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 08:03:53</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 08:03:53</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -849,54 +849,54 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IM204</t>
+          <t>AC714</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_BAIE</t>
+          <t>DIDEROT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IM204</t>
+          <t>AC714_1800</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:05:33</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:05:33</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -911,49 +911,49 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ET687</t>
+          <t>AC680</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DIEDROU</t>
+          <t>PK18_SICOGI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ET687</t>
+          <t>AC680_1800</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DAMBSC13</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:38:44</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:38:44</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -963,54 +963,54 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ET914</t>
+          <t>AC373</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_STADE</t>
+          <t>VESSO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ET914</t>
+          <t>AC373_900</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:28:11</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:28:11</t>
+          <t>2026-05-05 13:11:26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1020,54 +1020,54 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IM281</t>
+          <t>AC680</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_HERMANKONO</t>
+          <t>PK18_SICOGI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IM281</t>
+          <t>AC680_900</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>AOBSC06</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:28:17</t>
+          <t>2026-05-05 13:11:56</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:28:17</t>
+          <t>2026-05-05 13:11:56</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1077,54 +1077,54 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AC583</t>
+          <t>AC984</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KANAKONO</t>
+          <t>TCHEFRODOUO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AC583</t>
+          <t>AC984</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>AGBSC22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:11:23</t>
+          <t>2026-05-05 15:15:39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:11:23</t>
+          <t>2026-05-05 15:15:39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1134,54 +1134,54 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>DIABATE ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ET560</t>
+          <t>ET381</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BONOUA_DINGUI</t>
+          <t>CAFETOU</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ET560</t>
+          <t>ET381_900</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>AGBSC22</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:19:07</t>
+          <t>2026-05-05 15:45:39</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:19:07</t>
+          <t>2026-05-05 15:45:39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1196,49 +1196,49 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOU ANDRE YAO </t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ET361</t>
+          <t>ET514</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>OUARANIERE</t>
+          <t>PROLLO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ET361</t>
+          <t>ET514_900</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>YOBSC02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:45:59</t>
+          <t>2026-05-05 15:51:47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:45:59</t>
+          <t>2026-05-05 15:51:47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1248,54 +1248,54 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ET830</t>
+          <t>ET214</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TIORONIARADOUGOU</t>
+          <t>NERO_PALMCI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ET830</t>
+          <t>ET214</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>YOBSC02</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:46:16</t>
+          <t>2026-05-05 15:51:47</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:46:16</t>
+          <t>2026-05-05 15:51:47</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1305,54 +1305,54 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>AC601</t>
+          <t>AC278</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BKE_RUE_19</t>
+          <t>LAOGUIE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AC601</t>
+          <t>AC278_1800</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>SIBSC08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:27:18</t>
+          <t>2026-05-05 15:52:39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:27:18</t>
+          <t>2026-05-05 15:52:39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1367,49 +1367,49 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ET827</t>
+          <t>AC278</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO_VILLAGE CAN</t>
+          <t>LAOGUIE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ET827</t>
+          <t>AC278_900</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>SIBSC08</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:38:32</t>
+          <t>2026-05-05 15:52:39</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:38:37</t>
+          <t>2026-05-05 15:52:39</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1419,54 +1419,54 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AC486</t>
+          <t>AC544</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BROBO</t>
+          <t>CECHI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>AC486</t>
+          <t>AC544_900</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>SIBSC08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:15</t>
+          <t>2026-05-05 15:52:39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:20</t>
+          <t>2026-05-05 15:52:39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1481,49 +1481,49 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IM127</t>
+          <t>ET425</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BOBOKRO</t>
+          <t>KOUWEIT_PIERRE_GADIE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IM127</t>
+          <t>ET425_1800</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:16</t>
+          <t>2026-05-05 15:57:29</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:48:21</t>
+          <t>2026-05-05 15:57:29</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1538,49 +1538,49 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ET525</t>
+          <t>ET425</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>DAKOUPLEU</t>
+          <t>KOUWEIT_PIERRE_GADIE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ET525</t>
+          <t>ET425_900</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DAMBSC13</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:10:58</t>
+          <t>2026-05-05 15:57:29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:10:58</t>
+          <t>2026-05-05 15:57:29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IM429</t>
+          <t>ET252</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GADAGO_RURAL</t>
+          <t>GROBIAKOKO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>IM429</t>
+          <t>ET252_900</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>SIBSC08</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:03:25</t>
+          <t>2026-05-05 15:58:09</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:03:25</t>
+          <t>2026-05-05 15:58:09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1652,49 +1652,49 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>KONATE BAZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>IM414</t>
+          <t>AC522</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>RURAL_KENGUEMOUGOUSSO</t>
+          <t>IROBO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>IM414</t>
+          <t>AC522</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>YOBSC07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE ERIC HUB</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:58:41</t>
+          <t>2026-05-05 15:34:04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:58:41</t>
+          <t>2026-05-05 15:34:04</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1704,54 +1704,54 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ET974</t>
+          <t>ET172</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_GATL</t>
+          <t>SIPILOU</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ET974</t>
+          <t>ET172</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>DAMBSC13</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>MAN</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:35:34</t>
+          <t>2026-05-05 05:11:18</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:35:34</t>
+          <t>2026-05-05 05:11:23</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1766,49 +1766,49 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IM337</t>
+          <t>ET697</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TORKAHA</t>
+          <t>YORODOUGOU</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>IM337</t>
+          <t>ET697</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>DAMBSC13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>MAN</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:33:43</t>
+          <t>2026-05-05 05:48:25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:33:43</t>
+          <t>2026-05-05 05:48:25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1823,54 +1823,54 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>ET525</t>
+          <t>ET852</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DAKOUPLEU</t>
+          <t>TRAWAININKRO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>LET525</t>
+          <t>ET852</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DAKOUPLEU</t>
+          <t>YAMBSC12</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>ENODEB OUTAGE HUA</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:07:02</t>
+          <t>2026-05-05 10:24:28</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:07:05</t>
+          <t>2026-05-05 10:24:28</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -1880,29 +1880,29 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ET914</t>
+          <t>IM289</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_STADE</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>LET914</t>
+          <t>IM289</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_STADE</t>
+          <t>KOMBSC16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1912,22 +1912,22 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>ENODEB OUTAGE HUA</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:20:16</t>
+          <t>2026-05-05 11:56:30</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:20:19</t>
+          <t>2026-05-05 11:56:30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -1944,22 +1944,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ET041</t>
+          <t>ET064</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MICRO_AEROPORT</t>
+          <t>MONDOUKOU</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>LET041</t>
+          <t>ET064</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MICRO_AEROPORT</t>
+          <t>GBMBSC14</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1969,22 +1969,22 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>ENODEB OUTAGE HUA</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:23:42</t>
+          <t>2026-05-05 12:52:01</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:23:42</t>
+          <t>2026-05-05 12:54:01</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -1994,54 +1994,54 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t xml:space="preserve">ADOU ANDRE YAO </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ET366</t>
+          <t>ET064</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PORT_SPEDRO</t>
+          <t>MONDOUKOU</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>BB_ET366_W</t>
+          <t>ET064</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>YORNC02_RadioNode</t>
+          <t>MONDOUKOU</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:39:06</t>
+          <t>2026-05-05 12:59:56</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:39:06</t>
+          <t>2026-05-05 12:59:56</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2051,50 +2051,54 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t xml:space="preserve">ADOU ANDRE YAO </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ET366</t>
+          <t>ET124</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PORT_SPEDRO</t>
+          <t>KANZRA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>BB_ET366_GL</t>
-        </is>
-      </c>
-      <c r="D36" s="2"/>
+          <t>ET124</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>DALOA</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:39:17</t>
+          <t>2026-05-05 15:57:25</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:39:17</t>
+          <t>2026-05-05 15:57:25</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2104,107 +2108,87 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>ASSIE N'GUESSAN FRANCOIS</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>AC326</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>COPRIM</t>
-        </is>
-      </c>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>WAC326</t>
+          <t>IM161</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>SIRNC05_GROUP</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>ABIDJAN 02</t>
-        </is>
-      </c>
+          <t>KOMBSC16</t>
+        </is>
+      </c>
+      <c r="E37" s="2"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>CSL Fault</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:49:02</t>
+          <t>2026-05-02 20:09:11</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:49:02</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>3G</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>NO DG</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>TOURE HABIB ARMEL</t>
-        </is>
-      </c>
+          <t>2026-05-02 20:09:11</t>
+        </is>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AC326</t>
+          <t>IM429</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>COPRIM</t>
+          <t>GADAGO_RURAL</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>BB_AC326_GL</t>
-        </is>
-      </c>
-      <c r="D38" s="2"/>
+          <t>IM429</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>CSL Fault</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:53:10</t>
+          <t>2026-05-05 15:54:17</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:53:10</t>
+          <t>2026-05-05 15:54:17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2214,50 +2198,54 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>TOURE HABIB ARMEL</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ET690</t>
+          <t>ET974</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SP_STADE</t>
+          <t>ADJAHUI_GATL</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>BB_ET690_GL</t>
-        </is>
-      </c>
-      <c r="D39" s="2"/>
+          <t>LET974</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ADJAHUI_GATL</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE HUA</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:41:32</t>
+          <t>2026-05-04 18:51:19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:41:32</t>
+          <t>2026-05-04 18:51:22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2267,54 +2255,54 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ET690</t>
+          <t>ET064</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SP_STADE</t>
+          <t>MONDOUKOU</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>BB_ET690_W</t>
+          <t>LET064</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>YORNC02_RadioNode</t>
+          <t>MONDOUKOU</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE HUA</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:41:48</t>
+          <t>2026-05-05 12:57:14</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:41:48</t>
+          <t>2026-05-05 12:57:14</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2324,54 +2312,54 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t xml:space="preserve">ADOU ANDRE YAO </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ET187</t>
+          <t>ET702</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>HANNIE</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>WET187</t>
+          <t>LET702</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>YORNC02_GROUP</t>
+          <t>ROA</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE HUA</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:01:56</t>
+          <t>2026-05-05 13:13:53</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:03:47</t>
+          <t>2026-05-05 13:13:53</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2381,87 +2369,87 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ET184</t>
+          <t>AC311</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CARR_ZEGBAN</t>
+          <t>BKE_BELVILLE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>WET184</t>
+          <t>LAC311</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>YORNC07_GROUP</t>
+          <t>BKE_BELVILLE</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE HUA</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:23:40</t>
+          <t>2026-05-05 15:47:55</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:23:40</t>
+          <t>2026-05-05 15:51:16</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ET184</t>
+          <t>ET750</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CARR_ZEGBAN</t>
+          <t>MPOUTO_UACA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>BB_ET184_GL</t>
+          <t>BB_ET750_GL</t>
         </is>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2471,12 +2459,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:26:45</t>
+          <t>2026-05-05 00:32:34</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:26:45</t>
+          <t>2026-05-05 00:32:34</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2491,34 +2479,34 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ET935</t>
+          <t>ET750</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ANYAMA _CITEVERTE</t>
+          <t>MPOUTO_UACA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>BB_ET935_W</t>
+          <t>BB_ET750_W</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>AORNC06</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2528,12 +2516,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:41:50</t>
+          <t>2026-05-05 00:32:38</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:50:26</t>
+          <t>2026-05-05 00:32:38</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2548,30 +2536,30 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ET935</t>
+          <t>ET061</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ANYAMA _CITEVERTE</t>
+          <t>MBADON_EXTENSION</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>BB_ET935_GL</t>
+          <t>BB_ET061_GL</t>
         </is>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2581,12 +2569,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:41:50</t>
+          <t>2026-05-05 00:34:26</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:50:26</t>
+          <t>2026-05-05 00:34:26</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2601,34 +2589,34 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ET842</t>
+          <t>ET061</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>NIPLOU</t>
+          <t>MBADON_EXTENSION</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>BB_ET842_W</t>
+          <t>BB_ET061_W</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>YORNC02</t>
+          <t>ABRNC01_RadioNode</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2638,12 +2626,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:22:58</t>
+          <t>2026-05-05 00:34:34</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:22:58</t>
+          <t>2026-05-05 00:34:34</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2658,30 +2646,30 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ET842</t>
+          <t>AC726</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>NIPLOU</t>
+          <t>ANGRE_PRGRME6</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>BB_ET842_GL</t>
+          <t>BB_AC726_GL</t>
         </is>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2691,12 +2679,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:23:14</t>
+          <t>2026-05-05 06:57:03</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:23:14</t>
+          <t>2026-05-05 06:57:03</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2711,34 +2699,34 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ET219</t>
+          <t>AC726</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>SOKO</t>
+          <t>ANGRE_PRGRME6</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>BB_ET219_W</t>
+          <t>BB_AC726_W</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>AGRNC22_RadioNode</t>
+          <t>BVRNC04_RadioNode</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2748,12 +2736,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:36:42</t>
+          <t>2026-05-05 06:57:10</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:36:42</t>
+          <t>2026-05-05 06:57:10</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2768,30 +2756,34 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ET219</t>
+          <t>ET416</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SOKO</t>
+          <t>SAGBE_CELESTE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>BB_ET219_GL</t>
-        </is>
-      </c>
-      <c r="D49" s="2"/>
+          <t>WET416</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>AORNC06_GROUP</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2801,17 +2793,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:37:26</t>
+          <t>2026-05-05 08:28:07</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:37:26</t>
+          <t>2026-05-05 08:28:07</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2821,31 +2813,27 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>ET416</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MATENIN</t>
+          <t>SAGBE_CELESTE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>WAC377</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>AORNC06_GROUP</t>
-        </is>
-      </c>
+          <t>BB_ET416_GL</t>
+        </is>
+      </c>
+      <c r="D50" s="2"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>ABIDJAN 04</t>
@@ -2858,17 +2846,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:51:49</t>
+          <t>2026-05-05 08:31:35</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:51:49</t>
+          <t>2026-05-05 08:31:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2885,23 +2873,23 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AC374</t>
+          <t>ET493</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MATERNITE</t>
+          <t>ADIAPOTO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>BB_AC374_GL</t>
+          <t>LET493</t>
         </is>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2911,17 +2899,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:52:58</t>
+          <t>2026-05-05 10:45:58</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:52:58</t>
+          <t>2026-05-05 10:45:58</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2931,30 +2919,34 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>ET493</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MATENIN</t>
+          <t>ADIAPOTO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>BB_AC377_GL</t>
-        </is>
-      </c>
-      <c r="D52" s="2"/>
+          <t>BB_ET493_W</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>YORNC07_RadioNode</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2964,17 +2956,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:53:03</t>
+          <t>2026-05-05 10:50:22</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:53:03</t>
+          <t>2026-05-05 10:50:22</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2984,27 +2976,31 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ET418</t>
+          <t>ET713</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>AKEIKOI_GUEHABLE</t>
+          <t>ABOBO_SAGBE_RAIL</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>BB_ET418_GL</t>
-        </is>
-      </c>
-      <c r="D53" s="2"/>
+          <t>BB_ET713_W</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>AORNC06_RadioNode</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
           <t>ABIDJAN 04</t>
@@ -3017,17 +3013,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:53:10</t>
+          <t>2026-05-05 11:33:02</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:53:10</t>
+          <t>2026-05-05 11:33:02</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3037,31 +3033,27 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>KEKE TCHATCHA FERNANDEL</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ET418</t>
+          <t>ET713</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>AKEIKOI_GUEHABLE</t>
+          <t>ABOBO_SAGBE_RAIL</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>BB_ET418_W</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>AORNC06_RadioNode</t>
-        </is>
-      </c>
+          <t>BB_ET713_GL</t>
+        </is>
+      </c>
+      <c r="D54" s="2"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>ABIDJAN 04</t>
@@ -3074,17 +3066,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:53:23</t>
+          <t>2026-05-05 11:33:13</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:53:23</t>
+          <t>2026-05-05 11:33:13</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3094,225 +3086,221 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>KEKE TCHATCHA FERNANDEL</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ET474</t>
+          <t>AC373</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>DIO</t>
+          <t>VESSO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>DIO</t>
+          <t>WAC373</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DIO</t>
+          <t>AORNC06_GROUP</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 01:02:17</t>
+          <t>2026-05-05 13:14:47</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 01:02:17</t>
+          <t>2026-05-05 13:14:47</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IM276</t>
+          <t>AC373</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>DJELISSO_DIAWALA</t>
+          <t>VESSO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>DJELISSO_DIAWALA</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>DJELISSO_DIAWALA</t>
-        </is>
-      </c>
+          <t>BB_AC373_GL</t>
+        </is>
+      </c>
+      <c r="D56" s="2"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 08:07:22</t>
+          <t>2026-05-05 13:14:57</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 08:07:22</t>
+          <t>2026-05-05 13:14:57</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IM204</t>
+          <t>AC680</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_BAIE</t>
+          <t>PK18_SICOGI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_BAIE</t>
+          <t>WAC680</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_BAIE</t>
+          <t>AORNC06_GROUP</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:08:53</t>
+          <t>2026-05-05 13:15:14</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:08:53</t>
+          <t>2026-05-05 13:15:14</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ET687</t>
+          <t>AC714</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DIEDROU</t>
+          <t>DIDEROT</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>DIEDROU</t>
+          <t>BB_AC714_W</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>DIEDROU</t>
+          <t>AORNC06_RadioNode</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:41:54</t>
+          <t>2026-05-05 13:15:33</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:41:54</t>
+          <t>2026-05-05 13:15:33</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3322,54 +3310,50 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ET525</t>
+          <t>AC714</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>DAKOUPLEU</t>
+          <t>DIDEROT</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>DAKOUPLEU</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>DAKOUPLEU</t>
-        </is>
-      </c>
+          <t>BB_AC714_GL</t>
+        </is>
+      </c>
+      <c r="D59" s="2"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:14:23</t>
+          <t>2026-05-05 13:16:12</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:14:23</t>
+          <t>2026-05-05 13:16:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3379,111 +3363,103 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>IM429</t>
+          <t>AC680</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>GADAGO_RURAL</t>
+          <t>PK18_SICOGI</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>GADAGO_R</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>GADAGO_R</t>
-        </is>
-      </c>
+          <t>BB_AC680_GL</t>
+        </is>
+      </c>
+      <c r="D60" s="2"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:06:30</t>
+          <t>2026-05-05 13:18:12</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:06:30</t>
+          <t>2026-05-05 13:18:12</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ET914</t>
+          <t>ET948</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_STADE</t>
+          <t>BINGES_CITE_TRESOR</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_STADE</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>ODIENNE_STADE</t>
-        </is>
-      </c>
+          <t>BB_ET948_GL</t>
+        </is>
+      </c>
+      <c r="D61" s="2"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:31:27</t>
+          <t>2026-05-05 15:11:13</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:31:27</t>
+          <t>2026-05-05 15:11:13</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -3493,54 +3469,54 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>YAO KOUAKOU MARIUS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IM281</t>
+          <t>ET948</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_HERMANKONO</t>
+          <t>BINGES_CITE_TRESOR</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_HERMANKONO</t>
+          <t>BB_ET948_W</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_HERMANKONO</t>
+          <t>BVRNC04</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:31:30</t>
+          <t>2026-05-05 15:12:41</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:31:30</t>
+          <t>2026-05-05 15:12:41</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3550,54 +3526,54 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>YAO KOUAKOU MARIUS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AC583</t>
+          <t>ET063</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>KANAKONO</t>
+          <t>COCODY_MAIRIE</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>KANAKONO</t>
+          <t>BB_ET063_W</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>KANAKONO</t>
+          <t>MARNC21_RadioNode</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:14:30</t>
+          <t>2026-05-05 15:23:47</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:14:30</t>
+          <t>2026-05-05 15:23:47</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -3607,54 +3583,50 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>IM414</t>
+          <t>ET063</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>RURAL_KENGUEMOUGOUSSO</t>
+          <t>COCODY_MAIRIE</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>KENGUEMOUGOUSSO_R</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>KENGUEMOUGOUSSO_R</t>
-        </is>
-      </c>
+          <t>BB_ET063_GL</t>
+        </is>
+      </c>
+      <c r="D64" s="2"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:59:02</t>
+          <t>2026-05-05 15:24:43</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:59:02</t>
+          <t>2026-05-05 15:24:43</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -3664,54 +3636,54 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ET974</t>
+          <t>ET381</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_GATL</t>
+          <t>CAFETOU</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_GATL</t>
+          <t>WET381</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_GATL</t>
+          <t>AGRNC22_GROUP</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:38:42</t>
+          <t>2026-05-05 15:47:02</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:38:42</t>
+          <t>2026-05-05 15:47:02</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -3721,54 +3693,50 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ET560</t>
+          <t>ET381</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BONOUA_DINGUI</t>
+          <t>CAFETOU</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>BONOUA_CHATEAU</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>BONOUA_CHATEAU</t>
-        </is>
-      </c>
+          <t>BB_ET381_GL</t>
+        </is>
+      </c>
+      <c r="D66" s="2"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:22:29</t>
+          <t>2026-05-05 15:48:53</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:22:29</t>
+          <t>2026-05-05 15:48:53</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3778,54 +3746,54 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOU ANDRE YAO </t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ET830</t>
+          <t>IM040</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>TIORONIARADOUGOU</t>
+          <t>ABENG_ADOUKOFFIKRO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>TIORONIARADOUGOU</t>
+          <t>BB_IM040_GW</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>TIORONIARADOUGOU</t>
+          <t>AGRNC22</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:49:31</t>
+          <t>2026-05-05 15:49:38</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:49:31</t>
+          <t>2026-05-05 15:49:38</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -3835,168 +3803,160 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AC601</t>
+          <t>IM040</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>BKE_RUE_19</t>
+          <t>ABENG_ADOUKOFFIKRO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>BKE_RUE_19</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>BKE_RUE_19</t>
-        </is>
-      </c>
+          <t>BB_IM040_L</t>
+        </is>
+      </c>
+      <c r="D68" s="2"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:30:34</t>
+          <t>2026-05-05 15:50:16</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:30:34</t>
+          <t>2026-05-05 15:50:16</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>IM337</t>
+          <t>ET214</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>TORKAHA</t>
+          <t>NERO_PALMCI</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>TORKAHA_R</t>
+          <t>WET214</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>TORKAHA_R</t>
+          <t>YORNC02_GROUP</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:36:34</t>
+          <t>2026-05-05 15:52:01</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:36:34</t>
+          <t>2026-05-05 15:52:01</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ET361</t>
+          <t>IM011</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>OUARANIERE</t>
+          <t>KOBAKRO_ISRAEL</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>OUARANIERE</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>OUARANIERE</t>
-        </is>
-      </c>
+          <t>BB_IM011_L</t>
+        </is>
+      </c>
+      <c r="D70" s="2"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:37:03</t>
+          <t>2026-05-05 15:53:50</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:37:03</t>
+          <t>2026-05-05 15:53:50</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>3G,4G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -4006,54 +3966,54 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ET827</t>
+          <t>IM011</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO_VILLAGE CAN</t>
+          <t>KOBAKRO_ISRAEL</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>KOR_VILLAGE_CAN</t>
+          <t>BB_IM011_GW</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>KOR_VILLAGE_CAN</t>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:41:31</t>
+          <t>2026-05-05 15:53:51</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:41:31</t>
+          <t>2026-05-05 15:53:51</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -4063,54 +4023,50 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AC486</t>
+          <t>ET514</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>BROBO</t>
+          <t>PROLLO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>BROBO</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>BROBO</t>
-        </is>
-      </c>
+          <t>BB_ET514_GL</t>
+        </is>
+      </c>
+      <c r="D72" s="2"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:51:31</t>
+          <t>2026-05-05 15:55:22</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:51:31</t>
+          <t>2026-05-05 15:55:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -4120,163 +4076,159 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IM127</t>
+          <t>ET514</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>BOBOKRO</t>
+          <t>PROLLO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>BOBOKRO</t>
+          <t>BB_ET514_W</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>BOBOKRO</t>
+          <t>YORNC02_RadioNode</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:51:34</t>
+          <t>2026-05-05 15:55:29</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:51:34</t>
+          <t>2026-05-05 15:55:29</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AC629</t>
+          <t>ET214</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ASSONVON</t>
+          <t>NERO_PALMCI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>WAC629</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>YORNC02</t>
-        </is>
-      </c>
+          <t>BB_ET214_GL</t>
+        </is>
+      </c>
+      <c r="D74" s="2"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 12:52:56</t>
+          <t>2026-05-05 15:55:38</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 12:52:56</t>
+          <t>2026-05-05 15:55:38</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>TOURE HABIB ARMEL</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ET366</t>
+          <t>AC544</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>PORT_SPEDRO</t>
+          <t>CECHI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>BB_ET366_W</t>
+          <t>BB_AC544_W</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>YORNC02</t>
+          <t>SIRNC08_RadioNode</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:34:34</t>
+          <t>2026-05-05 15:56:25</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:34:34</t>
+          <t>2026-05-05 15:56:25</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4286,36 +4238,32 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AC054</t>
+          <t>AC278</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ETOILE</t>
+          <t>LAOGUIE</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>WAC054</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>AORNC06</t>
-        </is>
-      </c>
+          <t>BB_AC278_GL</t>
+        </is>
+      </c>
+      <c r="D76" s="2"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
           <t>ABIDJAN 04</t>
@@ -4323,22 +4271,22 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:02:18</t>
+          <t>2026-05-05 15:56:54</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:02:18</t>
+          <t>2026-05-05 15:56:54</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -4348,49 +4296,49 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>AC326</t>
+          <t>AC278</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>COPRIM</t>
+          <t>LAOGUIE</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>WAC326</t>
+          <t>BB_AC278_W</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>SIRNC05</t>
+          <t>AORNC09_RadioNode</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:51:09</t>
+          <t>2026-05-05 15:56:57</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:51:09</t>
+          <t>2026-05-05 15:56:57</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4400,116 +4348,108 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>TOURE HABIB ARMEL</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ET690</t>
+          <t>AC544</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SP_STADE</t>
+          <t>CECHI</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>BB_ET690_W</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>YORNC02</t>
-        </is>
-      </c>
+          <t>BB_AC544_GL</t>
+        </is>
+      </c>
+      <c r="D78" s="2"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:35:46</t>
+          <t>2026-05-05 15:57:21</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:35:46</t>
+          <t>2026-05-05 15:57:21</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ET187</t>
+          <t>IM150</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>HANNIE</t>
+          <t>ALLANY</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>WET187</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>YORNC02</t>
-        </is>
-      </c>
+          <t>BB_IM150_L</t>
+        </is>
+      </c>
+      <c r="D79" s="2"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 19:57:45</t>
+          <t>2026-05-05 15:57:34</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:02:15</t>
+          <t>2026-05-05 15:57:34</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -4519,29 +4459,29 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ET935</t>
+          <t>IM150</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ANYAMA _CITEVERTE</t>
+          <t>ALLANY</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>BB_ET935_W</t>
+          <t>BB_IM150_GW</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>AORNC06</t>
+          <t>AORNC09</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4551,17 +4491,17 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:12:25</t>
+          <t>2026-05-05 15:57:34</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:36:13</t>
+          <t>2026-05-05 15:57:34</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4576,111 +4516,87 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>ET450</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>SAYE</t>
-        </is>
-      </c>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>BB_ET450_W</t>
+          <t>SEGUELON</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>ABENGOUROU</t>
-        </is>
-      </c>
+          <t>SEGUELON</t>
+        </is>
+      </c>
+      <c r="E81" s="2"/>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:07:50</t>
+          <t>2026-05-02 20:13:50</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:58:29</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>3G</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>NO DG</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>DIABATE ABDOULAYE</t>
-        </is>
-      </c>
+          <t>2026-05-02 20:13:50</t>
+        </is>
+      </c>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ET842</t>
+          <t>ET172</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>NIPLOU</t>
+          <t>SIPILOU</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>BB_ET842_W</t>
+          <t>SIPILOU_NEW</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>YORNC02</t>
+          <t>SIPILOU_NEW</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>MAN</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:17:25</t>
+          <t>2026-05-05 05:14:30</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:17:25</t>
+          <t>2026-05-05 05:14:30</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -4690,54 +4606,54 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ET219</t>
+          <t>ET697</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SOKO</t>
+          <t>YORODOUGOU</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>BB_ET219_W</t>
+          <t>YORODOUGOU</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
+          <t>YORODOUGOU</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>MAN</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:34:37</t>
+          <t>2026-05-05 05:51:30</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:34:37</t>
+          <t>2026-05-05 05:51:30</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -4747,54 +4663,54 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>AC377</t>
+          <t>ET852</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>MATENIN</t>
+          <t>TRAWAININKRO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>WAC377</t>
+          <t>TRAVAININKRO</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>AORNC06</t>
+          <t>TRAVAININKRO</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:50:57</t>
+          <t>2026-05-05 10:27:26</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:50:57</t>
+          <t>2026-05-05 10:27:26</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4804,29 +4720,29 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>ET474</t>
+          <t>IM289</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>DIO</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>WET474</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>DAMBSC13</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4836,22 +4752,22 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:57:39</t>
+          <t>2026-05-05 11:55:06</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:57:39</t>
+          <t>2026-05-05 11:55:06</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4868,47 +4784,47 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>IM276</t>
+          <t>IM429</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>DJELISSO_DIAWALA</t>
+          <t>GADAGO_RURAL</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>WIM276</t>
+          <t>GADAGO_R</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>GADAGO_R</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 08:02:31</t>
+          <t>2026-05-05 15:57:38</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 08:02:31</t>
+          <t>2026-05-05 15:57:38</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4918,49 +4834,49 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>IM204</t>
+          <t>ET452</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_BAIE</t>
+          <t>TAKIKRO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>WIM204</t>
+          <t>BB_ET452_W</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>AGRNC22</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:04:15</t>
+          <t>2026-05-04 15:26:30</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:04:15</t>
+          <t>2026-05-05 00:40:47</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4975,49 +4891,49 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ET687</t>
+          <t>ET750</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>DIEDROU</t>
+          <t>MPOUTO_UACA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>WET687</t>
+          <t>BB_ET750_W</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DAMBSC13</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:37:23</t>
+          <t>2026-05-05 00:35:28</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:37:23</t>
+          <t>2026-05-05 00:35:28</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5032,49 +4948,49 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>IM281</t>
+          <t>ET061</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_HERMANKONO</t>
+          <t>MBADON_EXTENSION</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>WIM281</t>
+          <t>BB_ET061_W</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:26:50</t>
+          <t>2026-05-05 00:35:32</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:26:50</t>
+          <t>2026-05-05 00:35:32</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5089,49 +5005,49 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ET914</t>
+          <t>AC726</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ODIENNE_STADE</t>
+          <t>ANGRE_PRGRME6</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>WET914</t>
+          <t>BB_AC726_W</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>BVRNC04</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:26:52</t>
+          <t>2026-05-05 06:55:03</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:26:52</t>
+          <t>2026-05-05 06:55:03</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5146,49 +5062,49 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>AC583</t>
+          <t>ET025</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>KANAKONO</t>
+          <t>RESDCE_KIMI3</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>WAC583</t>
+          <t>WET025</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>ABRNC03</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:10:00</t>
+          <t>2026-05-05 06:59:22</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:10:00</t>
+          <t>2026-05-05 06:59:22</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5203,49 +5119,49 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>SYLVAIN SOMPLEI</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AC148</t>
+          <t>IM297</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>YABAYO</t>
+          <t>BAIE_COCODY_GOLF</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>WAC148</t>
+          <t>BB_IM297_GW</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:43:51</t>
+          <t>2026-05-05 07:00:34</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:44:35</t>
+          <t>2026-05-05 07:00:34</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5255,54 +5171,54 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>AC165</t>
+          <t>ET416</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>BONOUA</t>
+          <t>SAGBE_CELESTE</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>WET560</t>
+          <t>WET416</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:48</t>
+          <t>2026-05-05 08:29:56</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:17:48</t>
+          <t>2026-05-05 08:29:56</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5312,54 +5228,54 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADOU ANDRE YAO </t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ET830</t>
+          <t>ET713</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>TIORONIARADOUGOU</t>
+          <t>ABOBO_SAGBE_RAIL</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>WET830</t>
+          <t>BB_ET713_W</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:44:52</t>
+          <t>2026-05-05 11:27:53</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:44:52</t>
+          <t>2026-05-05 11:27:53</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5374,49 +5290,49 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AC601</t>
+          <t>AC714</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>BKE_RUE_19</t>
+          <t>DIDEROT</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>WAC601</t>
+          <t>BB_AC714_W</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:25:59</t>
+          <t>2026-05-05 13:10:39</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:25:59</t>
+          <t>2026-05-05 13:10:39</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5426,54 +5342,54 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ET361</t>
+          <t>ET948</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>OUARANIERE</t>
+          <t>BINGES_CITE_TRESOR</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>WET361</t>
+          <t>BB_ET948_W</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>BVRNC04</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:32:12</t>
+          <t>2026-05-05 15:09:09</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:32:12</t>
+          <t>2026-05-05 15:09:09</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5488,49 +5404,49 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>YAO KOUAKOU MARIUS</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AC486</t>
+          <t>ET097</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>BROBO</t>
+          <t>ABENG_AGNI_EXT</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>WAC486</t>
+          <t>BB_ET097_W</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>AGRNC22</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:46:55</t>
+          <t>2026-05-05 15:43:36</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:46:55</t>
+          <t>2026-05-05 15:43:36</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5540,54 +5456,54 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>N'GORAN KONAN RENAUD</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>IM127</t>
+          <t>IM040</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>BOBOKRO</t>
+          <t>ABENG_ADOUKOFFIKRO</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>WIM127</t>
+          <t>BB_IM040_GW</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>AGRNC22</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:46:55</t>
+          <t>2026-05-05 15:43:36</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:46:55</t>
+          <t>2026-05-05 15:43:36</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5602,49 +5518,49 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ET525</t>
+          <t>IM011</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>DAKOUPLEU</t>
+          <t>KOBAKRO_ISRAEL</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>WET525</t>
+          <t>BB_IM011_GW</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>DAMBSC13</t>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>NodeB Unavailable</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:09:37</t>
+          <t>2026-05-05 15:48:14</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:09:37</t>
+          <t>2026-05-05 15:48:14</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5659,49 +5575,49 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>IM429</t>
+          <t>ET381</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GADAGO_RURAL</t>
+          <t>CAFETOU</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>WIM429</t>
+          <t>WET381</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>AGRNC22</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>NodeB Unavailable</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:02:07</t>
+          <t>2026-05-05 15:50:39</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 14:02:07</t>
+          <t>2026-05-05 15:50:39</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5716,49 +5632,49 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>DIARRASSOUBA ZOUMANA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>IM414</t>
+          <t>AC544</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>RURAL_KENGUEMOUGOUSSO</t>
+          <t>CECHI</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>WIM414</t>
+          <t>BB_AC544_W</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>BKMBSC15</t>
+          <t>SIRNC08</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>NodeB Unavailable</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:52:32</t>
+          <t>2026-05-05 15:51:34</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 17:52:32</t>
+          <t>2026-05-05 15:51:34</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5768,54 +5684,54 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>KEKE TCHATCHA FERNANDEL</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ET974</t>
+          <t>ET050</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>ADJAHUI_GATL</t>
+          <t>SONGON_HEVEA</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>WET974</t>
+          <t>BB_ET050_W</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>YORNC07</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>NodeB Unavailable</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:34:15</t>
+          <t>2026-05-05 15:57:32</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 21:34:15</t>
+          <t>2026-05-05 15:57:33</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5830,49 +5746,49 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>IM337</t>
+          <t>ET214</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>TORKAHA</t>
+          <t>NERO_PALMCI</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>WIM337</t>
+          <t>WET214</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>YORNC02</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>NodeB Unavailable</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:32:10</t>
+          <t>2026-05-05 15:57:32</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:32:10</t>
+          <t>2026-05-05 15:57:32</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5882,69 +5798,501 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>KONE MOHAMED LAMINE</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ET827</t>
+          <t>ET514</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>KORHOGO_VILLAGE CAN</t>
+          <t>PROLLO</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>WET827</t>
+          <t>BB_ET514_W</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>YORNC02</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>SAN-PEDRO</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE ERIC</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:57:46</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:57:46</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>OUATTARA MOUMINI</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>AC039</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>CARNOT</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>WAC039</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>YORNC07</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>ABIDJAN 02</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE ERIC HUB</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 21:06:56</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 21:06:57</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>GNAORE DIDI ERIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ET172</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SIPILOU</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>WET172</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 05:09:58</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 05:09:58</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>YEO DOSONGUY ABRAHAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ET697</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>YORODOUGOU</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>WET697</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 05:47:07</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 05:47:07</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>YEO DOSONGUY ABRAHAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ET852</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>TRAWAININKRO</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>WET852</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 10:23:05</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 10:23:05</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>GAUZE GUINANDE DAMIEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>IM289</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>KOLIKO</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>WIM289</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
           <t>KOMBSC16</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>KORHOGO</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:09:04</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:09:04</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>YEO DOSONGUY ABRAHAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>ET064</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>MONDOUKOU</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>WET064</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>MONDOUKOU</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>ABIDJAN 01</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:59:06</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:59:06</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADOU ANDRE YAO </t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>WIM161</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>KOMBSC16</t>
+        </is>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>NodeB Unavailable</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30 00:37:06</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30 00:37:06</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 20:07:56</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 20:07:56</t>
+        </is>
+      </c>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>IM429</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>GADAGO_RURAL</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>WIM429</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>NodeB Unavailable</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:52:56</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 15:52:56</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>3G</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>NO DG</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>KONE MOHAMED LAMINE</t>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
     </row>
